--- a/FREVS/westwood hills.xlsx
+++ b/FREVS/westwood hills.xlsx
@@ -674,9 +674,9 @@
           <t>In-place annual rent</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" t="n" s="9">
         <f>B7*B9*12*B8</f>
-        <v/>
+        <v>6299868.96</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -727,9 +727,9 @@
           <t>Expense ratio used for this property</t>
         </is>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" t="n" s="12">
         <f>B13/B14</f>
-        <v/>
+        <v>0.4216229089</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -743,9 +743,9 @@
           <t>Estimated NOI</t>
         </is>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" t="n" s="9">
         <f>B10*(1-B15)</f>
-        <v/>
+        <v>3643699.8836935167</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Same labeled LOW cap rate as the brooks.xlsx (5.5% row).</t>
+          <t>LOW cap rate is 6.0%, widened from the brooks.xlsx 5.5% row.</t>
         </is>
       </c>
     </row>
@@ -947,20 +947,20 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LOW, 5.5%</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
+          <t>LOW, 6.0%</t>
+        </is>
+      </c>
+      <c r="B33" t="n" s="8">
         <f>B19</f>
-        <v/>
-      </c>
-      <c r="C33" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="C33" t="n" s="9">
         <f>$B$16/B33</f>
-        <v/>
-      </c>
-      <c r="D33" s="14">
+        <v>60728331.3948919475</v>
+      </c>
+      <c r="D33" t="n" s="14">
         <f>C33/$B$25-1</f>
-        <v/>
+        <v>7.0254171263</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <f>B20</f>
         <v/>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" t="n" s="9">
         <f>$B$16/B34</f>
-        <v/>
-      </c>
-      <c r="D34" s="14">
+        <v>72873997.6738703251</v>
+      </c>
+      <c r="D34" t="n" s="14">
         <f>C34/$B$25-1</f>
-        <v/>
+        <v>8.6305005516</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Value = estimated NOI ÷ cap rate, before depreciation and before the mortgage. That is the same relationship as the brooks.xlsx (NOI divided by the cap rate) and as upton place - Valuation.xlsx. LOW uses 5.5% and HIGH uses 5.0%, the rows labeled LOW and HIGH on the brooks.xlsx. The 5.6% and 5.63% rows are shown and are not the LOW or HIGH that the investment case reads. Operating expense is the residential segment ratio, because this property's own expenses are not disclosed.</t>
+          <t>Value = estimated NOI ÷ cap rate, before depreciation and before the mortgage. That is the same relationship as the brooks.xlsx (NOI divided by the cap rate) and as upton place - Valuation.xlsx. LOW uses 6.0%, widened from the brooks.xlsx 5.5% row, and HIGH uses 5.0%, the HIGH row on the brooks.xlsx. The 5.6% and 5.63% rows are shown and are not the LOW or HIGH that the investment case reads. Operating expense is the residential segment ratio, because this property's own expenses are not disclosed.</t>
         </is>
       </c>
     </row>
@@ -1086,9 +1086,9 @@
           <t>Ownership</t>
         </is>
       </c>
-      <c r="B101" s="18">
+      <c r="B101" t="n" s="18">
         <f>B5</f>
-        <v/>
+        <v>0.4</v>
       </c>
     </row>
     <row r="102">
@@ -1097,9 +1097,9 @@
           <t>Book carrying value</t>
         </is>
       </c>
-      <c r="B102" s="19">
+      <c r="B102" t="n" s="19">
         <f>B25</f>
-        <v/>
+        <v>7567000</v>
       </c>
     </row>
     <row r="103">
@@ -1108,9 +1108,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="B103" s="19">
+      <c r="B103" t="n" s="19">
         <f>C33</f>
-        <v/>
+        <v>60728331.3948919475</v>
       </c>
     </row>
     <row r="104">
@@ -1119,9 +1119,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="B104" s="19">
+      <c r="B104" t="n" s="19">
         <f>C34</f>
-        <v/>
+        <v>72873997.6738703251</v>
       </c>
     </row>
     <row r="105">
@@ -1140,9 +1140,9 @@
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="B106" s="19">
+      <c r="B106" t="n" s="19">
         <f>B26</f>
-        <v/>
+        <v>24541000</v>
       </c>
     </row>
     <row r="107">
@@ -1151,9 +1151,9 @@
           <t>NOI used</t>
         </is>
       </c>
-      <c r="B107" s="19">
+      <c r="B107" t="n" s="19">
         <f>B16</f>
-        <v/>
+        <v>3643699.8836935167</v>
       </c>
     </row>
     <row r="108">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>Method: in-place rent × (1 − residential segment expense ratio), divided by the brooks.xlsx 5.5% / 5.0% cap rates. The investment case then takes 40%. NOI is not filed for this property.</t>
+          <t>Method: in-place rent × (1 − residential segment expense ratio), divided by a 6.0% LOW cap rate and the brooks.xlsx 5.0% HIGH cap rate. The investment case then takes 40%. NOI is not filed for this property.</t>
         </is>
       </c>
     </row>
